--- a/upload/baselegal_reducaocalculo.xlsx
+++ b/upload/baselegal_reducaocalculo.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="39">
   <si>
     <t>Item do Anexo I, 
 Decreto nº 47.394/2018</t>
@@ -247,7 +247,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="23">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -274,15 +274,6 @@
       </left>
       <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
@@ -507,17 +498,6 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
         <color indexed="64"/>
       </left>
       <right/>
@@ -532,71 +512,92 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="19" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -604,38 +605,8 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="7" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="20" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -921,255 +892,279 @@
   <dimension ref="A1:D22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.28515625" style="8" customWidth="1"/>
-    <col min="3" max="3" width="35.7109375" style="8" customWidth="1"/>
-    <col min="4" max="4" width="34.7109375" style="8" customWidth="1"/>
+    <col min="1" max="1" width="18.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.28515625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="35.7109375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="34.7109375" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="11"/>
-    </row>
-    <row r="2" spans="1:4" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="21"/>
+    </row>
+    <row r="2" spans="1:4" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="13"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="14"/>
-      <c r="B3" s="15" t="s">
+      <c r="D2" s="23"/>
+    </row>
+    <row r="3" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="6"/>
+      <c r="B3" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
+      <c r="D3" s="24"/>
+    </row>
+    <row r="4" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="4" t="s">
+      <c r="B4" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="4"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="14"/>
-      <c r="B5" s="16"/>
-      <c r="C5" s="4" t="s">
+      <c r="D4" s="25"/>
+    </row>
+    <row r="5" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="6"/>
+      <c r="B5" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="4"/>
-    </row>
-    <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="17">
+      <c r="D5" s="25"/>
+    </row>
+    <row r="6" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="7">
         <v>11</v>
       </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="4" t="s">
+      <c r="B6" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="4"/>
-    </row>
-    <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="17">
+      <c r="D6" s="25"/>
+    </row>
+    <row r="7" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="7">
         <v>34</v>
       </c>
-      <c r="B7" s="16"/>
-      <c r="C7" s="4" t="s">
+      <c r="B7" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="4"/>
-    </row>
-    <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="17">
+      <c r="D7" s="25"/>
+    </row>
+    <row r="8" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="7">
         <v>35</v>
       </c>
-      <c r="B8" s="16"/>
-      <c r="C8" s="4" t="s">
+      <c r="B8" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="4"/>
+      <c r="D8" s="25"/>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="17">
+      <c r="A9" s="7">
         <v>63</v>
       </c>
-      <c r="B9" s="18"/>
-      <c r="C9" s="5" t="s">
+      <c r="B9" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="5"/>
+      <c r="D9" s="32"/>
     </row>
     <row r="10" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17"/>
-      <c r="B10" s="19" t="s">
+      <c r="A10" s="7"/>
+      <c r="B10" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="21"/>
+      <c r="D10" s="27"/>
     </row>
     <row r="11" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="17"/>
-      <c r="B11" s="22" t="s">
+      <c r="A11" s="7"/>
+      <c r="B11" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="24"/>
+      <c r="D11" s="29"/>
     </row>
     <row r="12" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="17"/>
-      <c r="B12" s="19" t="s">
+      <c r="A12" s="7"/>
+      <c r="B12" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="21"/>
+      <c r="D12" s="27"/>
     </row>
     <row r="13" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="17"/>
-      <c r="B13" s="22" t="s">
+      <c r="A13" s="7"/>
+      <c r="B13" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="26"/>
-    </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="17"/>
-      <c r="B14" s="15" t="s">
+      <c r="D13" s="31"/>
+    </row>
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="7"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="7"/>
+      <c r="B15" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="28" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="17"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="29" t="s">
+      <c r="C15" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D15" s="30" t="s">
+      <c r="D15" s="12" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="17"/>
-      <c r="B16" s="16"/>
-      <c r="C16" s="29" t="s">
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="7"/>
+      <c r="B16" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="D16" s="30" t="s">
+      <c r="D16" s="12" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="17">
+    <row r="17" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="7">
         <v>327</v>
       </c>
-      <c r="B17" s="16"/>
-      <c r="C17" s="29" t="s">
+      <c r="B17" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="D17" s="31" t="s">
+      <c r="D17" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="17">
+    <row r="18" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="7">
         <v>329</v>
       </c>
-      <c r="B18" s="16"/>
-      <c r="C18" s="6" t="s">
+      <c r="B18" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="31" t="s">
+      <c r="D18" s="13" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="17">
+    <row r="19" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="7">
         <v>330</v>
       </c>
-      <c r="B19" s="16"/>
-      <c r="C19" s="6" t="s">
+      <c r="B19" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D19" s="31" t="s">
+      <c r="D19" s="13" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="32"/>
-      <c r="B20" s="16"/>
-      <c r="C20" s="6" t="s">
+    <row r="20" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="14"/>
+      <c r="B20" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D20" s="30" t="s">
+      <c r="D20" s="12" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="33"/>
-      <c r="B21" s="16"/>
-      <c r="C21" s="6" t="s">
+    <row r="21" spans="1:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="15"/>
+      <c r="B21" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D21" s="30" t="s">
+      <c r="D21" s="12" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="34"/>
-      <c r="B22" s="35"/>
-      <c r="C22" s="6" t="s">
+    <row r="22" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="16"/>
+      <c r="B22" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D22" s="30" t="s">
+      <c r="D22" s="12" t="s">
         <v>38</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="B3:B9"/>
-    <mergeCell ref="B14:B22"/>
+  <mergeCells count="13">
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:D9"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C9:D9"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D17" r:id="rId1" location="parte1it52" display="Item 52, Anexo II"/>
